--- a/excels/minerva_terrestre_exportaciones.xlsx
+++ b/excels/minerva_terrestre_exportaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ale\zz_ale_cosas\otras_personas\Pirazzoli\pirazzoli-demo\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7529EF61-B600-4B5D-A729-4535B93B65CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47286356-97DF-4BA9-BD9A-0E451F5AC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7618C72B-C967-4346-827E-EFA46EAC6289}"/>
   </bookViews>

--- a/excels/minerva_terrestre_exportaciones.xlsx
+++ b/excels/minerva_terrestre_exportaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ale\zz_ale_cosas\otras_personas\Pirazzoli\pirazzoli-demo\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47286356-97DF-4BA9-BD9A-0E451F5AC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609764CE-DFFF-465F-9461-B7742848F0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7618C72B-C967-4346-827E-EFA46EAC6289}"/>
   </bookViews>
@@ -4815,6 +4815,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FFC29204"/>
       <color rgb="FFFADE8C"/>
       <color rgb="FFFAE298"/>
@@ -19737,7 +19738,7 @@
       <formula>NOT(ISERROR(SEARCH("PENDIENTE",AD1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="4">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K73" xr:uid="{D1BD1D09-B747-4B08-82C5-94745BB3340D}">
       <formula1>TIPO_CARGA</formula1>
     </dataValidation>
@@ -30589,21 +30590,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004762AEE074382F459D1866064B8447D4" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="fbcb6eca3569625aa3da17f0ecd31501">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4662f0e3-f4c4-4931-8e76-960ae722852f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="63821c1fe76ba995fd6cb1d2c442ca7a" ns2:_="">
     <xsd:import namespace="4662f0e3-f4c4-4931-8e76-960ae722852f"/>
@@ -30741,24 +30727,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{183E6228-D059-4D4A-9844-9FB7E4EC7682}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{695864D4-4D75-4318-98FB-08B4DB48CFF6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9733FB95-B7F1-4430-9D8C-98621A69FCF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30774,4 +30758,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{695864D4-4D75-4318-98FB-08B4DB48CFF6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{183E6228-D059-4D4A-9844-9FB7E4EC7682}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/excels/minerva_terrestre_exportaciones.xlsx
+++ b/excels/minerva_terrestre_exportaciones.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ale\zz_ale_cosas\otras_personas\Pirazzoli\pirazzoli-demo\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609764CE-DFFF-465F-9461-B7742848F0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8E5883-EAE4-4D42-9613-A5E096E02B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7618C72B-C967-4346-827E-EFA46EAC6289}"/>
   </bookViews>
   <sheets>
-    <sheet name="IMPO TERR" sheetId="1" r:id="rId1"/>
+    <sheet name="EXPO TERR" sheetId="1" r:id="rId1"/>
     <sheet name="CERTIFICACIONES" sheetId="7" r:id="rId2"/>
     <sheet name="Matriz datos" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CERTIFICACIONES!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IMPO TERR'!$A$1:$AH$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EXPO TERR'!$A$1:$AH$1</definedName>
     <definedName name="CARGA">'Matriz datos'!$B$2:$B$9</definedName>
     <definedName name="cliente">'Matriz datos'!$J$2:$J$11</definedName>
     <definedName name="INSTRUCCIONES">'Matriz datos'!$G$2:$G$3</definedName>
@@ -5348,7 +5348,7 @@
         <v>48</v>
       </c>
       <c r="U2" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T2,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T2,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. GALVARINO 8601 BGA. 11, QUILICURA</v>
       </c>
       <c r="V2" s="82" t="s">
@@ -5443,7 +5443,7 @@
         <v>60</v>
       </c>
       <c r="U3" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T3,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T3,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO SANTA MARTA 2101, MAIPU</v>
       </c>
       <c r="V3" s="83" t="s">
@@ -5538,7 +5538,7 @@
         <v>68</v>
       </c>
       <c r="U4" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T4,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T4,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V4" s="155" t="s">
@@ -5627,7 +5627,7 @@
         <v>68</v>
       </c>
       <c r="U5" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T5,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T5,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V5" s="235" t="s">
@@ -5718,7 +5718,7 @@
         <v>68</v>
       </c>
       <c r="U6" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T6,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T6,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V6" s="156" t="s">
@@ -5807,7 +5807,7 @@
         <v>88</v>
       </c>
       <c r="U7" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T7,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T7,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V7" s="90" t="s">
@@ -5896,7 +5896,7 @@
         <v>68</v>
       </c>
       <c r="U8" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T8,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T8,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V8" s="235" t="s">
@@ -5989,7 +5989,7 @@
         <v>68</v>
       </c>
       <c r="U9" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T9,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T9,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V9" s="157" t="s">
@@ -6078,7 +6078,7 @@
         <v>68</v>
       </c>
       <c r="U10" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T10,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T10,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V10" s="72"/>
@@ -6163,7 +6163,7 @@
         <v>88</v>
       </c>
       <c r="U11" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T11,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T11,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V11" s="70" t="s">
@@ -6254,7 +6254,7 @@
         <v>68</v>
       </c>
       <c r="U12" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T12,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T12,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V12" s="74" t="s">
@@ -6343,7 +6343,7 @@
         <v>68</v>
       </c>
       <c r="U13" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T13,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T13,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V13" s="74"/>
@@ -6428,7 +6428,7 @@
         <v>68</v>
       </c>
       <c r="U14" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T14,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T14,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V14" s="74"/>
@@ -6515,7 +6515,7 @@
         <v>68</v>
       </c>
       <c r="U15" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T15,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T15,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V15" s="74"/>
@@ -6604,7 +6604,7 @@
         <v>68</v>
       </c>
       <c r="U16" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T16,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T16,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V16" s="74"/>
@@ -6687,7 +6687,7 @@
         <v>68</v>
       </c>
       <c r="U17" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T17,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T17,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V17" s="74" t="s">
@@ -6776,7 +6776,7 @@
         <v>148</v>
       </c>
       <c r="U18" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T18,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T18,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. EL PARRON 345, LA CISTERNA</v>
       </c>
       <c r="V18" s="74"/>
@@ -6861,7 +6861,7 @@
         <v>68</v>
       </c>
       <c r="U19" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T19,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T19,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V19" s="74"/>
@@ -6946,7 +6946,7 @@
         <v>88</v>
       </c>
       <c r="U20" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T20,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T20,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="W20" s="71"/>
@@ -7030,7 +7030,7 @@
         <v>148</v>
       </c>
       <c r="U21" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T21,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T21,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. EL PARRON 345, LA CISTERNA</v>
       </c>
       <c r="W21" s="71"/>
@@ -7116,7 +7116,7 @@
         <v>68</v>
       </c>
       <c r="U22" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T22,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T22,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V22" s="70" t="s">
@@ -7295,7 +7295,7 @@
         <v>88</v>
       </c>
       <c r="U24" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T24,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T24,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="W24" s="71"/>
@@ -7381,7 +7381,7 @@
         <v>68</v>
       </c>
       <c r="U25" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T25,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T25,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W25" s="71"/>
@@ -7465,7 +7465,7 @@
         <v>68</v>
       </c>
       <c r="U26" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T26,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T26,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V26" s="70" t="s">
@@ -7554,7 +7554,7 @@
         <v>68</v>
       </c>
       <c r="U27" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T27,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T27,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W27" s="71"/>
@@ -7638,7 +7638,7 @@
         <v>68</v>
       </c>
       <c r="U28" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T28,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T28,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W28" s="71"/>
@@ -7720,7 +7720,7 @@
         <v>68</v>
       </c>
       <c r="U29" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T29,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T29,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W29" s="71"/>
@@ -7802,7 +7802,7 @@
         <v>68</v>
       </c>
       <c r="U30" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T30,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T30,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V30" s="70" t="s">
@@ -7891,7 +7891,7 @@
         <v>88</v>
       </c>
       <c r="U31" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T31,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T31,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="W31" s="71"/>
@@ -7973,7 +7973,7 @@
         <v>88</v>
       </c>
       <c r="U32" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T32,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T32,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V32" s="76" t="s">
@@ -8060,7 +8060,7 @@
         <v>68</v>
       </c>
       <c r="U33" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T33,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T33,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V33" s="70" t="s">
@@ -8149,7 +8149,7 @@
         <v>68</v>
       </c>
       <c r="U34" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T34,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T34,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V34" s="77" t="s">
@@ -8236,7 +8236,7 @@
         <v>68</v>
       </c>
       <c r="U35" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T35,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T35,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V35" s="78" t="s">
@@ -8325,7 +8325,7 @@
         <v>68</v>
       </c>
       <c r="U36" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T36,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T36,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V36" s="70" t="s">
@@ -8411,7 +8411,7 @@
         <v>68</v>
       </c>
       <c r="U37" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T37,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T37,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V37" s="70" t="s">
@@ -8498,7 +8498,7 @@
         <v>252</v>
       </c>
       <c r="U38" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T38,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T38,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="W38" s="71"/>
@@ -8580,7 +8580,7 @@
         <v>68</v>
       </c>
       <c r="U39" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T39,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T39,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V39" s="70" t="s">
@@ -8669,7 +8669,7 @@
         <v>68</v>
       </c>
       <c r="U40" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T40,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T40,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V40" s="70" t="s">
@@ -8758,7 +8758,7 @@
         <v>68</v>
       </c>
       <c r="U41" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T41,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T41,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V41" s="93" t="s">
@@ -8845,7 +8845,7 @@
         <v>68</v>
       </c>
       <c r="U42" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T42,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T42,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V42" s="93"/>
@@ -8928,7 +8928,7 @@
         <v>88</v>
       </c>
       <c r="U43" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T43,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T43,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V43" s="70" t="s">
@@ -9015,7 +9015,7 @@
         <v>68</v>
       </c>
       <c r="U44" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T44,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T44,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V44" s="70" t="s">
@@ -9102,7 +9102,7 @@
         <v>68</v>
       </c>
       <c r="U45" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T45,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T45,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W45" s="71"/>
@@ -9184,7 +9184,7 @@
         <v>88</v>
       </c>
       <c r="U46" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T46,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T46,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V46" s="70" t="s">
@@ -9271,7 +9271,7 @@
         <v>299</v>
       </c>
       <c r="U47" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T47,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T47,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V47" s="93" t="s">
@@ -9360,7 +9360,7 @@
         <v>306</v>
       </c>
       <c r="U48" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T48,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T48,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CORDILLERA 451, QUILICURA</v>
       </c>
       <c r="V48" s="76" t="s">
@@ -9447,7 +9447,7 @@
         <v>68</v>
       </c>
       <c r="U49" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T49,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T49,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V49" s="235" t="s">
@@ -9534,7 +9534,7 @@
         <v>68</v>
       </c>
       <c r="U50" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T50,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T50,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V50" s="78" t="s">
@@ -9623,7 +9623,7 @@
         <v>68</v>
       </c>
       <c r="U51" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T51,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T51,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V51" s="70" t="s">
@@ -9714,7 +9714,7 @@
         <v>88</v>
       </c>
       <c r="U52" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T51,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T51,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V52" s="70" t="s">
@@ -9891,7 +9891,7 @@
         <v>88</v>
       </c>
       <c r="U54" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T54,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T54,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V54" s="70" t="s">
@@ -9982,7 +9982,7 @@
         <v>299</v>
       </c>
       <c r="U55" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T55,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T55,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V55" s="70" t="s">
@@ -10071,7 +10071,7 @@
         <v>148</v>
       </c>
       <c r="U56" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T56,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T56,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. EL PARRON 345, LA CISTERNA</v>
       </c>
       <c r="V56" s="70" t="s">
@@ -10158,7 +10158,7 @@
         <v>299</v>
       </c>
       <c r="U57" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T57,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T57,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V57" s="70" t="s">
@@ -10247,7 +10247,7 @@
         <v>371</v>
       </c>
       <c r="U58" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T58,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T58,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>6 ORIENTE 152-D CALETERA ORIENTE ALTURA KM 39, PAINE</v>
       </c>
       <c r="V58" s="70" t="s">
@@ -10334,7 +10334,7 @@
         <v>68</v>
       </c>
       <c r="U59" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T59,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T59,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V59" s="70" t="s">
@@ -10419,7 +10419,7 @@
         <v>60</v>
       </c>
       <c r="U60" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T60,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T60,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO SANTA MARTA 2101, MAIPU</v>
       </c>
       <c r="V60" s="70" t="s">
@@ -10505,7 +10505,7 @@
         <v>68</v>
       </c>
       <c r="U61" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T61,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T61,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V61" s="70" t="s">
@@ -10583,7 +10583,7 @@
         <v>68</v>
       </c>
       <c r="U62" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T62,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T62,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V62" s="70" t="s">
@@ -10755,7 +10755,7 @@
         <v>68</v>
       </c>
       <c r="U64" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T64,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T64,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V64" s="70" t="s">
@@ -10843,7 +10843,7 @@
         <v>68</v>
       </c>
       <c r="U65" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T65,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T65,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V65" s="70" t="s">
@@ -10934,7 +10934,7 @@
         <v>68</v>
       </c>
       <c r="U66" s="103" t="str">
-        <f>VLOOKUP('IMPO TERR'!T66,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T66,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V66" s="70" t="s">
@@ -11110,7 +11110,7 @@
         <v>68</v>
       </c>
       <c r="U68" s="170" t="str">
-        <f>VLOOKUP('IMPO TERR'!T68,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T68,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V68" s="70" t="s">
@@ -11199,7 +11199,7 @@
         <v>60</v>
       </c>
       <c r="U69" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T69,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T69,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO SANTA MARTA 2101, MAIPU</v>
       </c>
       <c r="V69" s="70" t="s">
@@ -11289,7 +11289,7 @@
         <v>68</v>
       </c>
       <c r="U70" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T70,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T70,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V70" s="70" t="s">
@@ -11380,7 +11380,7 @@
         <v>68</v>
       </c>
       <c r="U71" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T71,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T71,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V71" s="70" t="s">
@@ -11468,7 +11468,7 @@
         <v>68</v>
       </c>
       <c r="U72" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T72,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T72,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V72" s="83" t="s">
@@ -11559,7 +11559,7 @@
         <v>299</v>
       </c>
       <c r="U73" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T73,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T73,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V73" s="83" t="s">
@@ -11652,7 +11652,7 @@
         <v>60</v>
       </c>
       <c r="U74" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T74,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T74,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO SANTA MARTA 2101, MAIPU</v>
       </c>
       <c r="V74" s="70" t="s">
@@ -11739,7 +11739,7 @@
         <v>299</v>
       </c>
       <c r="U75" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T75,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T75,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V75" s="70" t="s">
@@ -11918,7 +11918,7 @@
         <v>68</v>
       </c>
       <c r="U77" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T77,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T77,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V77" s="70" t="s">
@@ -12002,7 +12002,7 @@
         <v>68</v>
       </c>
       <c r="U78" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T78,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T78,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V78" s="70" t="s">
@@ -12086,7 +12086,7 @@
         <v>68</v>
       </c>
       <c r="U79" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T79,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T79,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V79" s="70" t="s">
@@ -12175,7 +12175,7 @@
         <v>68</v>
       </c>
       <c r="U80" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T80,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T80,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V80" s="70" t="s">
@@ -12264,7 +12264,7 @@
         <v>88</v>
       </c>
       <c r="U81" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T81,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T81,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V81" s="90" t="s">
@@ -12353,7 +12353,7 @@
         <v>68</v>
       </c>
       <c r="U82" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T82,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T82,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V82" s="235" t="s">
@@ -12438,7 +12438,7 @@
         <v>68</v>
       </c>
       <c r="U83" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T83,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T83,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V83" s="235" t="s">
@@ -12524,7 +12524,7 @@
         <v>68</v>
       </c>
       <c r="U84" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T84,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T84,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V84" s="70" t="s">
@@ -12613,7 +12613,7 @@
         <v>68</v>
       </c>
       <c r="U85" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T85,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T85,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V85" s="70" t="s">
@@ -12700,7 +12700,7 @@
         <v>88</v>
       </c>
       <c r="U86" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T86,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T86,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V86" s="90" t="s">
@@ -12778,7 +12778,7 @@
         <v>68</v>
       </c>
       <c r="U87" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T87,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T87,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V87" s="235" t="s">
@@ -12867,7 +12867,7 @@
         <v>306</v>
       </c>
       <c r="U88" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T88,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T88,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CORDILLERA 451, QUILICURA</v>
       </c>
       <c r="V88" s="275" t="s">
@@ -12958,7 +12958,7 @@
         <v>148</v>
       </c>
       <c r="U89" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T89,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T89,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. EL PARRON 345, LA CISTERNA</v>
       </c>
       <c r="V89" s="275" t="s">
@@ -13045,7 +13045,7 @@
         <v>68</v>
       </c>
       <c r="U90" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T90,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T90,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V90" s="35" t="s">
@@ -13123,7 +13123,7 @@
         <v>299</v>
       </c>
       <c r="U91" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T91,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T91,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V91" s="83" t="s">
@@ -13208,7 +13208,7 @@
         <v>88</v>
       </c>
       <c r="U92" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T92,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T92,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V92" s="83" t="s">
@@ -13282,7 +13282,7 @@
         <v>68</v>
       </c>
       <c r="U93" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T93,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T93,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V93" s="90" t="s">
@@ -13356,7 +13356,7 @@
         <v>68</v>
       </c>
       <c r="U94" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T94,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T94,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V94" s="235" t="s">
@@ -13434,7 +13434,7 @@
         <v>68</v>
       </c>
       <c r="U95" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T95,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T95,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V95" s="94" t="s">
@@ -13520,7 +13520,7 @@
         <v>68</v>
       </c>
       <c r="U96" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T96,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T96,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V96" s="83" t="s">
@@ -13602,7 +13602,7 @@
         <v>68</v>
       </c>
       <c r="U97" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T97,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T97,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V97" s="95" t="s">
@@ -13680,7 +13680,7 @@
         <v>485</v>
       </c>
       <c r="U98" s="8" t="e">
-        <f>VLOOKUP('IMPO TERR'!T98,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T98,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>#N/A</v>
       </c>
       <c r="V98" s="83" t="s">
@@ -13766,7 +13766,7 @@
         <v>68</v>
       </c>
       <c r="U99" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T99,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T99,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V99" s="76" t="s">
@@ -13852,7 +13852,7 @@
         <v>60</v>
       </c>
       <c r="U100" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T100,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T100,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO SANTA MARTA 2101, MAIPU</v>
       </c>
       <c r="V100" s="235" t="s">
@@ -13941,7 +13941,7 @@
         <v>148</v>
       </c>
       <c r="U101" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T101,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T101,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. EL PARRON 345, LA CISTERNA</v>
       </c>
       <c r="V101" s="275" t="s">
@@ -14027,7 +14027,7 @@
         <v>148</v>
       </c>
       <c r="U102" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T102,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T102,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. EL PARRON 345, LA CISTERNA</v>
       </c>
       <c r="V102" s="275" t="s">
@@ -14116,7 +14116,7 @@
         <v>68</v>
       </c>
       <c r="U103" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T103,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T103,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V103" s="78" t="s">
@@ -14198,7 +14198,7 @@
         <v>68</v>
       </c>
       <c r="U104" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T104,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T104,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V104" s="70" t="s">
@@ -14284,7 +14284,7 @@
         <v>68</v>
       </c>
       <c r="U105" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T105,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T105,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W105" s="71"/>
@@ -14365,7 +14365,7 @@
         <v>68</v>
       </c>
       <c r="U106" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T106,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T106,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W106" s="71"/>
@@ -14442,7 +14442,7 @@
         <v>68</v>
       </c>
       <c r="U107" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T107,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T107,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V107" s="70" t="s">
@@ -14516,7 +14516,7 @@
         <v>88</v>
       </c>
       <c r="U108" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T108,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T108,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V108" s="70" t="s">
@@ -14594,7 +14594,7 @@
         <v>88</v>
       </c>
       <c r="U109" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T109,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T109,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V109" s="70" t="s">
@@ -14680,7 +14680,7 @@
         <v>88</v>
       </c>
       <c r="U110" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T110,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T110,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V110" s="70" t="s">
@@ -14764,7 +14764,7 @@
         <v>68</v>
       </c>
       <c r="U111" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T111,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T111,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V111" s="70" t="s">
@@ -14838,7 +14838,7 @@
         <v>68</v>
       </c>
       <c r="U112" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T112,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T112,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V112" s="70" t="s">
@@ -14996,7 +14996,7 @@
         <v>68</v>
       </c>
       <c r="U114" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T114,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T114,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V114" s="70" t="s">
@@ -15072,7 +15072,7 @@
         <v>68</v>
       </c>
       <c r="U115" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T115,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T115,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V115" s="70" t="s">
@@ -15153,7 +15153,7 @@
         <v>68</v>
       </c>
       <c r="U116" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T116,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T116,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W116" s="71"/>
@@ -15224,7 +15224,7 @@
         <v>88</v>
       </c>
       <c r="U117" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T117,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T117,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V117" s="163"/>
@@ -15304,7 +15304,7 @@
         <v>299</v>
       </c>
       <c r="U118" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T118,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T118,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V118" s="162" t="s">
@@ -15391,7 +15391,7 @@
         <v>68</v>
       </c>
       <c r="U119" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T119,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T119,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V119" s="78" t="s">
@@ -15479,7 +15479,7 @@
         <v>736</v>
       </c>
       <c r="U120" s="8" t="e">
-        <f>VLOOKUP('IMPO TERR'!T120,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T120,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>#N/A</v>
       </c>
       <c r="V120" s="70" t="s">
@@ -15563,7 +15563,7 @@
         <v>88</v>
       </c>
       <c r="U121" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T121,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T121,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V121" s="70" t="s">
@@ -15643,7 +15643,7 @@
         <v>68</v>
       </c>
       <c r="U122" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T122,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T122,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V122" s="70" t="s">
@@ -15715,7 +15715,7 @@
         <v>88</v>
       </c>
       <c r="U123" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T123,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T123,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V123" s="70" t="s">
@@ -15791,7 +15791,7 @@
         <v>88</v>
       </c>
       <c r="U124" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T124,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T124,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="V124" s="70" t="s">
@@ -15871,7 +15871,7 @@
         <v>68</v>
       </c>
       <c r="U125" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T125,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T125,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V125" s="70" t="s">
@@ -15939,7 +15939,7 @@
         <v>88</v>
       </c>
       <c r="U126" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T126,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T126,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. AMERICO VESPUCIO 0350, QUILICURA</v>
       </c>
       <c r="W126" s="71"/>
@@ -16006,7 +16006,7 @@
         <v>299</v>
       </c>
       <c r="U127" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T127,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T127,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V127" s="70" t="s">
@@ -16078,7 +16078,7 @@
         <v>68</v>
       </c>
       <c r="U128" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T128,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T128,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V128" s="70" t="s">
@@ -16150,7 +16150,7 @@
         <v>68</v>
       </c>
       <c r="U129" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T129,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T129,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V129" s="70" t="s">
@@ -16226,7 +16226,7 @@
         <v>68</v>
       </c>
       <c r="U130" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T130,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T130,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W130" s="71"/>
@@ -16297,7 +16297,7 @@
         <v>68</v>
       </c>
       <c r="U131" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T131,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T131,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="W131" s="71"/>
@@ -16368,7 +16368,7 @@
         <v>299</v>
       </c>
       <c r="U132" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T132,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T132,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>CAMINO LO AGUIRRE SUR 537, PUDAHUEL </v>
       </c>
       <c r="V132" s="70" t="s">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="T133" s="12"/>
       <c r="U133" s="8" t="e">
-        <f>VLOOKUP('IMPO TERR'!T133,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T133,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>#N/A</v>
       </c>
       <c r="V133" s="70" t="s">
@@ -16516,7 +16516,7 @@
         <v>68</v>
       </c>
       <c r="U134" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T134,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T134,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V134" s="70" t="s">
@@ -16586,7 +16586,7 @@
         <v>68</v>
       </c>
       <c r="U135" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T135,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T135,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V135" s="35" t="s">
@@ -16658,7 +16658,7 @@
         <v>68</v>
       </c>
       <c r="U136" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T136,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T136,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V136" s="70" t="s">
@@ -16728,7 +16728,7 @@
         <v>68</v>
       </c>
       <c r="U137" s="8" t="str">
-        <f>VLOOKUP('IMPO TERR'!T137,'Matriz datos'!$J$2:$K$10,2,0)</f>
+        <f>VLOOKUP('EXPO TERR'!T137,'Matriz datos'!$J$2:$K$10,2,0)</f>
         <v>AV. PDTE. EDUARDO FREI 8301, QUILICURA</v>
       </c>
       <c r="V137" s="172" t="s">
@@ -30590,6 +30590,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004762AEE074382F459D1866064B8447D4" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="fbcb6eca3569625aa3da17f0ecd31501">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4662f0e3-f4c4-4931-8e76-960ae722852f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="63821c1fe76ba995fd6cb1d2c442ca7a" ns2:_="">
     <xsd:import namespace="4662f0e3-f4c4-4931-8e76-960ae722852f"/>
@@ -30727,22 +30742,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{183E6228-D059-4D4A-9844-9FB7E4EC7682}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{695864D4-4D75-4318-98FB-08B4DB48CFF6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9733FB95-B7F1-4430-9D8C-98621A69FCF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30758,21 +30775,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{695864D4-4D75-4318-98FB-08B4DB48CFF6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{183E6228-D059-4D4A-9844-9FB7E4EC7682}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>